--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_o_higgins.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_o_higgins.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.50658429720971</v>
+      </c>
+      <c r="C2">
         <v>26.66124549415606</v>
-      </c>
-      <c r="C2">
-        <v>27.50658429720971</v>
       </c>
       <c r="D2">
         <v>3.75076250739746</v>
       </c>
       <c r="E2">
-        <v>17.29365038752672</v>
+        <v>17.84197412289852</v>
       </c>
       <c r="F2">
         <v>64.86437548957477</v>
       </c>
       <c r="G2">
-        <v>17.84197412289852</v>
+        <v>17.29365038752672</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>26.78039844286696</v>
+      </c>
+      <c r="C3">
         <v>28.72681474696588</v>
-      </c>
-      <c r="C3">
-        <v>26.78039844286696</v>
       </c>
       <c r="D3">
         <v>3.481068154643284</v>
       </c>
       <c r="E3">
-        <v>18.4729789427183</v>
+        <v>17.22132233838905</v>
       </c>
       <c r="F3">
         <v>64.30569871889266</v>
       </c>
       <c r="G3">
-        <v>17.22132233838905</v>
+        <v>18.4729789427183</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>28.63315897202638</v>
+      </c>
+      <c r="C4">
         <v>37.00250170570843</v>
-      </c>
-      <c r="C4">
-        <v>28.63315897202638</v>
       </c>
       <c r="D4">
         <v>2.702519975414874</v>
       </c>
       <c r="E4">
-        <v>22.33969518055746</v>
+        <v>17.28683234930661</v>
       </c>
       <c r="F4">
         <v>60.37347247013594</v>
       </c>
       <c r="G4">
-        <v>17.28683234930661</v>
+        <v>22.33969518055746</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>29.74076983503535</v>
+      </c>
+      <c r="C5">
         <v>31.84603299293008</v>
-      </c>
-      <c r="C5">
-        <v>29.74076983503535</v>
       </c>
       <c r="D5">
         <v>3.140108534780464</v>
       </c>
       <c r="E5">
-        <v>19.70831307729704</v>
+        <v>18.40544482255713</v>
       </c>
       <c r="F5">
         <v>61.88624210014585</v>
       </c>
       <c r="G5">
-        <v>18.40544482255713</v>
+        <v>19.70831307729704</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>31.1045871559633</v>
+      </c>
+      <c r="C6">
         <v>29.37981651376147</v>
-      </c>
-      <c r="C6">
-        <v>31.1045871559633</v>
       </c>
       <c r="D6">
         <v>3.40369722707969</v>
       </c>
       <c r="E6">
-        <v>18.30696057806641</v>
+        <v>19.38168846611177</v>
       </c>
       <c r="F6">
         <v>62.31135095582182</v>
       </c>
       <c r="G6">
-        <v>19.38168846611177</v>
+        <v>18.30696057806641</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>30.71567931890741</v>
+      </c>
+      <c r="C7">
         <v>25.11528910961334</v>
-      </c>
-      <c r="C7">
-        <v>30.71567931890741</v>
       </c>
       <c r="D7">
         <v>3.981638418079096</v>
       </c>
       <c r="E7">
-        <v>16.11700765444043</v>
+        <v>19.7108954841647</v>
       </c>
       <c r="F7">
         <v>64.17209686139488</v>
       </c>
       <c r="G7">
-        <v>19.7108954841647</v>
+        <v>16.11700765444043</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>29.17352233894444</v>
+      </c>
+      <c r="C8">
         <v>30.66067586381471</v>
-      </c>
-      <c r="C8">
-        <v>29.17352233894444</v>
       </c>
       <c r="D8">
         <v>3.261506707946336</v>
       </c>
       <c r="E8">
+        <v>18.25236568080136</v>
+      </c>
+      <c r="F8">
+        <v>62.56483351150176</v>
+      </c>
+      <c r="G8">
         <v>19.18280080769688</v>
-      </c>
-      <c r="F8">
-        <v>62.56483351150177</v>
-      </c>
-      <c r="G8">
-        <v>18.25236568080136</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>33.22961471584149</v>
+      </c>
+      <c r="C9">
         <v>21.81751624416583</v>
-      </c>
-      <c r="C9">
-        <v>33.22961471584149</v>
       </c>
       <c r="D9">
         <v>4.583473154362416</v>
       </c>
       <c r="E9">
-        <v>14.0715381891158</v>
+        <v>21.43194428048637</v>
       </c>
       <c r="F9">
-        <v>64.49651753039782</v>
+        <v>64.49651753039784</v>
       </c>
       <c r="G9">
-        <v>21.43194428048636</v>
+        <v>14.07153818911581</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>26.21860305080858</v>
+      </c>
+      <c r="C10">
         <v>33.18041059754559</v>
-      </c>
-      <c r="C10">
-        <v>26.21860305080858</v>
       </c>
       <c r="D10">
         <v>3.013826477704804</v>
       </c>
       <c r="E10">
+        <v>16.4484098431429</v>
+      </c>
+      <c r="F10">
+        <v>62.7356454166067</v>
+      </c>
+      <c r="G10">
         <v>20.81594474025039</v>
-      </c>
-      <c r="F10">
-        <v>62.73564541660671</v>
-      </c>
-      <c r="G10">
-        <v>16.4484098431429</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>31.18714741231298</v>
+      </c>
+      <c r="C11">
         <v>28.30512631837135</v>
-      </c>
-      <c r="C11">
-        <v>31.18714741231298</v>
       </c>
       <c r="D11">
         <v>3.532928942807626</v>
       </c>
       <c r="E11">
-        <v>17.74702037677816</v>
+        <v>19.55401768550558</v>
       </c>
       <c r="F11">
         <v>62.69896193771626</v>
       </c>
       <c r="G11">
-        <v>19.55401768550558</v>
+        <v>17.74702037677816</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>28.83449359982034</v>
+      </c>
+      <c r="C12">
         <v>28.85695037053672</v>
-      </c>
-      <c r="C12">
-        <v>28.83449359982034</v>
       </c>
       <c r="D12">
         <v>3.465369649805448</v>
       </c>
       <c r="E12">
-        <v>18.2996297351182</v>
+        <v>18.28538877812589</v>
       </c>
       <c r="F12">
         <v>63.41498148675591</v>
       </c>
       <c r="G12">
-        <v>18.28538877812589</v>
+        <v>18.2996297351182</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>26.03004291845494</v>
+      </c>
+      <c r="C13">
         <v>31.95278969957081</v>
-      </c>
-      <c r="C13">
-        <v>26.03004291845494</v>
       </c>
       <c r="D13">
         <v>3.12961719274681</v>
       </c>
       <c r="E13">
-        <v>20.2254822059223</v>
+        <v>16.47650095082858</v>
       </c>
       <c r="F13">
         <v>63.29801684324912</v>
       </c>
       <c r="G13">
-        <v>16.47650095082858</v>
+        <v>20.2254822059223</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>27.12841507227003</v>
+      </c>
+      <c r="C14">
         <v>33.92096248642326</v>
-      </c>
-      <c r="C14">
-        <v>27.12841507227003</v>
       </c>
       <c r="D14">
         <v>2.948029556650246</v>
       </c>
       <c r="E14">
-        <v>21.06246109151276</v>
+        <v>16.84478107491181</v>
       </c>
       <c r="F14">
         <v>62.09275783357543</v>
       </c>
       <c r="G14">
-        <v>16.84478107491181</v>
+        <v>21.06246109151276</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>25.64333071131588</v>
+      </c>
+      <c r="C15">
         <v>30.07079447128891</v>
-      </c>
-      <c r="C15">
-        <v>25.64333071131588</v>
       </c>
       <c r="D15">
         <v>3.325485799701046</v>
       </c>
       <c r="E15">
-        <v>19.31153929421953</v>
+        <v>16.46821101248466</v>
       </c>
       <c r="F15">
         <v>64.22024969329581</v>
       </c>
       <c r="G15">
-        <v>16.46821101248466</v>
+        <v>19.31153929421953</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>28.46680182463254</v>
+      </c>
+      <c r="C16">
         <v>27.75975671566143</v>
-      </c>
-      <c r="C16">
-        <v>28.46680182463254</v>
       </c>
       <c r="D16">
         <v>3.602337045828008</v>
       </c>
       <c r="E16">
-        <v>17.76891008483787</v>
+        <v>18.22148685256379</v>
       </c>
       <c r="F16">
         <v>64.00960306259834</v>
       </c>
       <c r="G16">
-        <v>18.22148685256379</v>
+        <v>17.76891008483787</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>28.3360444980847</v>
+      </c>
+      <c r="C17">
         <v>25.1246261216351</v>
-      </c>
-      <c r="C17">
-        <v>28.3360444980847</v>
       </c>
       <c r="D17">
         <v>3.98015873015873</v>
       </c>
       <c r="E17">
-        <v>16.3720294067362</v>
+        <v>18.46469481962729</v>
       </c>
       <c r="F17">
         <v>65.16327577363651</v>
       </c>
       <c r="G17">
-        <v>18.46469481962729</v>
+        <v>16.3720294067362</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>26.71174142480211</v>
+      </c>
+      <c r="C18">
         <v>32.70778364116095</v>
-      </c>
-      <c r="C18">
-        <v>26.71174142480211</v>
       </c>
       <c r="D18">
         <v>3.057376222647978</v>
       </c>
       <c r="E18">
-        <v>20.51679907315458</v>
+        <v>16.75562727573651</v>
       </c>
       <c r="F18">
         <v>62.72757365110891</v>
       </c>
       <c r="G18">
-        <v>16.75562727573651</v>
+        <v>20.51679907315458</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>25.91906085881989</v>
+      </c>
+      <c r="C19">
         <v>29.5798578931109</v>
-      </c>
-      <c r="C19">
-        <v>25.91906085881989</v>
       </c>
       <c r="D19">
         <v>3.380678851174935</v>
       </c>
       <c r="E19">
-        <v>19.02254892222112</v>
+        <v>16.6683222409854</v>
       </c>
       <c r="F19">
         <v>64.30912883679348</v>
       </c>
       <c r="G19">
-        <v>16.6683222409854</v>
+        <v>19.02254892222112</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>29.1866028708134</v>
+      </c>
+      <c r="C20">
         <v>44.81658692185008</v>
-      </c>
-      <c r="C20">
-        <v>29.1866028708134</v>
       </c>
       <c r="D20">
         <v>2.231316725978647</v>
       </c>
       <c r="E20">
-        <v>25.75618698441797</v>
+        <v>16.77360219981668</v>
       </c>
       <c r="F20">
         <v>57.47021081576536</v>
       </c>
       <c r="G20">
-        <v>16.77360219981668</v>
+        <v>25.75618698441797</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>29.17357328913095</v>
+      </c>
+      <c r="C21">
         <v>36.51432630831163</v>
-      </c>
-      <c r="C21">
-        <v>29.17357328913095</v>
       </c>
       <c r="D21">
         <v>2.738651102464332</v>
       </c>
       <c r="E21">
-        <v>22.03801629269687</v>
+        <v>17.60754609118193</v>
       </c>
       <c r="F21">
         <v>60.35443761612119</v>
       </c>
       <c r="G21">
-        <v>17.60754609118193</v>
+        <v>22.03801629269687</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>22.48698438125751</v>
+      </c>
+      <c r="C22">
         <v>35.28233880656788</v>
-      </c>
-      <c r="C22">
-        <v>22.48698438125751</v>
       </c>
       <c r="D22">
         <v>2.83427922814983</v>
       </c>
       <c r="E22">
-        <v>22.3632440665059</v>
+        <v>14.25307780175149</v>
       </c>
       <c r="F22">
         <v>63.38367813174261</v>
       </c>
       <c r="G22">
-        <v>14.25307780175149</v>
+        <v>22.3632440665059</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>30.81207856933451</v>
+      </c>
+      <c r="C23">
         <v>51.04075051304603</v>
-      </c>
-      <c r="C23">
-        <v>30.81207856933451</v>
       </c>
       <c r="D23">
         <v>1.959218839747272</v>
       </c>
       <c r="E23">
-        <v>28.06706432371433</v>
+        <v>16.94341447686603</v>
       </c>
       <c r="F23">
         <v>54.98952119941963</v>
       </c>
       <c r="G23">
-        <v>16.94341447686603</v>
+        <v>28.06706432371433</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>22.2106901920083</v>
+      </c>
+      <c r="C24">
         <v>40.8406850025947</v>
-      </c>
-      <c r="C24">
-        <v>22.2106901920083</v>
       </c>
       <c r="D24">
         <v>2.44853875476493</v>
       </c>
       <c r="E24">
+        <v>13.62189688096754</v>
+      </c>
+      <c r="F24">
+        <v>61.33036282622534</v>
+      </c>
+      <c r="G24">
         <v>25.04774029280713</v>
-      </c>
-      <c r="F24">
-        <v>61.33036282622533</v>
-      </c>
-      <c r="G24">
-        <v>13.62189688096754</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>27.00610835870193</v>
+      </c>
+      <c r="C25">
         <v>27.77810939334249</v>
-      </c>
-      <c r="C25">
-        <v>27.00610835870193</v>
       </c>
       <c r="D25">
         <v>3.599957023135878</v>
       </c>
       <c r="E25">
-        <v>17.94634478680601</v>
+        <v>17.44758525831373</v>
       </c>
       <c r="F25">
         <v>64.60606995488025</v>
       </c>
       <c r="G25">
-        <v>17.44758525831373</v>
+        <v>17.94634478680601</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>31.47307739482399</v>
+      </c>
+      <c r="C26">
         <v>35.71691401937937</v>
-      </c>
-      <c r="C26">
-        <v>31.47307739482399</v>
       </c>
       <c r="D26">
         <v>2.799793956043956</v>
       </c>
       <c r="E26">
-        <v>21.3630694739931</v>
+        <v>18.82473773017387</v>
       </c>
       <c r="F26">
         <v>59.81219279583303</v>
       </c>
       <c r="G26">
-        <v>18.82473773017387</v>
+        <v>21.3630694739931</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>28.60131630562699</v>
+      </c>
+      <c r="C27">
         <v>29.1374275378111</v>
-      </c>
-      <c r="C27">
-        <v>28.60131630562699</v>
       </c>
       <c r="D27">
         <v>3.432011967090501</v>
       </c>
       <c r="E27">
-        <v>18.47195357833655</v>
+        <v>18.13208068527217</v>
       </c>
       <c r="F27">
         <v>63.39596573639126</v>
       </c>
       <c r="G27">
-        <v>18.13208068527217</v>
+        <v>18.47195357833655</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>26.69950738916256</v>
+      </c>
+      <c r="C28">
         <v>38.69458128078818</v>
-      </c>
-      <c r="C28">
-        <v>26.69950738916256</v>
       </c>
       <c r="D28">
         <v>2.584341183959262</v>
       </c>
       <c r="E28">
-        <v>23.39538346984363</v>
+        <v>16.14296351451973</v>
       </c>
       <c r="F28">
         <v>60.46165301563663</v>
       </c>
       <c r="G28">
-        <v>16.14296351451973</v>
+        <v>23.39538346984363</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>29.03819604233778</v>
+      </c>
+      <c r="C29">
         <v>30.483202945237</v>
-      </c>
-      <c r="C29">
-        <v>29.03819604233778</v>
       </c>
       <c r="D29">
         <v>3.280495169082126</v>
       </c>
       <c r="E29">
-        <v>19.10916224324948</v>
+        <v>18.20332333256405</v>
       </c>
       <c r="F29">
         <v>62.68751442418648</v>
       </c>
       <c r="G29">
-        <v>18.20332333256405</v>
+        <v>19.10916224324948</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>25.68306010928962</v>
+      </c>
+      <c r="C30">
         <v>32.92700014011489</v>
-      </c>
-      <c r="C30">
-        <v>25.68306010928962</v>
       </c>
       <c r="D30">
         <v>3.037021276595745</v>
       </c>
       <c r="E30">
-        <v>20.75971731448763</v>
+        <v>16.19257950530035</v>
       </c>
       <c r="F30">
         <v>63.04770318021201</v>
       </c>
       <c r="G30">
-        <v>16.19257950530035</v>
+        <v>20.75971731448763</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>25.21391112337841</v>
+      </c>
+      <c r="C31">
         <v>32.88711012972674</v>
-      </c>
-      <c r="C31">
-        <v>25.21391112337841</v>
       </c>
       <c r="D31">
         <v>3.040704993705413</v>
       </c>
       <c r="E31">
-        <v>20.80132681564246</v>
+        <v>15.94797486033519</v>
       </c>
       <c r="F31">
         <v>63.25069832402234</v>
       </c>
       <c r="G31">
-        <v>15.94797486033519</v>
+        <v>20.80132681564246</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>26.20775084055919</v>
+      </c>
+      <c r="C32">
         <v>31.33958591399752</v>
-      </c>
-      <c r="C32">
-        <v>26.20775084055919</v>
       </c>
       <c r="D32">
         <v>3.190852625635234</v>
       </c>
       <c r="E32">
-        <v>19.89217117825453</v>
+        <v>16.6348421880265</v>
       </c>
       <c r="F32">
         <v>63.47298663371897</v>
       </c>
       <c r="G32">
-        <v>16.6348421880265</v>
+        <v>19.89217117825453</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>24.90196078431373</v>
+      </c>
+      <c r="C33">
         <v>47.99019607843137</v>
-      </c>
-      <c r="C33">
-        <v>24.90196078431373</v>
       </c>
       <c r="D33">
         <v>2.083758937691522</v>
       </c>
       <c r="E33">
-        <v>27.75730082222852</v>
+        <v>14.40317550326056</v>
       </c>
       <c r="F33">
         <v>57.83952367451091</v>
       </c>
       <c r="G33">
-        <v>14.40317550326056</v>
+        <v>27.75730082222852</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>26.15641115117677</v>
+      </c>
+      <c r="C34">
         <v>29.48703035942771</v>
-      </c>
-      <c r="C34">
-        <v>26.15641115117677</v>
       </c>
       <c r="D34">
         <v>3.391321499013807</v>
       </c>
       <c r="E34">
-        <v>18.94524438244233</v>
+        <v>16.80534103931045</v>
       </c>
       <c r="F34">
         <v>64.24941457824723</v>
       </c>
       <c r="G34">
-        <v>16.80534103931045</v>
+        <v>18.94524438244233</v>
       </c>
     </row>
   </sheetData>
